--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,6 +909,965 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121667584</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92029</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Färnebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>363685</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6388490</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121667580</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98110</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Färnebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>363797</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6388525</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121667579</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98110</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Färnebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>363799</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6388526</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 15 plantor</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121667576</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98110</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Färnebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>363802</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6388528</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 plantor</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121667578</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98110</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Färnebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>363780</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6388524</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4 plantor</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121667582</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98110</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Färnebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>363788</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6388516</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121667583</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98110</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Färnebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>363792</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6388513</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121667575</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98144</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Färnebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>363843</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6388553</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 planta</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121667577</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98110</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Färnebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>363776</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6388511</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Seglora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 35 plantor</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121667584</v>
+        <v>121667577</v>
       </c>
       <c r="B4" t="n">
-        <v>92029</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,25 +923,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363685</v>
+        <v>363776</v>
       </c>
       <c r="R4" t="n">
-        <v>6388490</v>
+        <v>6388511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,12 +981,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,17 +1011,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667580</v>
+        <v>121667575</v>
       </c>
       <c r="B5" t="n">
-        <v>98110</v>
+        <v>98147</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363797</v>
+        <v>363843</v>
       </c>
       <c r="R5" t="n">
-        <v>6388525</v>
+        <v>6388553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,6 +1107,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,17 +1119,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667579</v>
+        <v>121667584</v>
       </c>
       <c r="B6" t="n">
-        <v>98110</v>
+        <v>92032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1138,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363799</v>
+        <v>363685</v>
       </c>
       <c r="R6" t="n">
-        <v>6388526</v>
+        <v>6388490</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,17 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca 15 plantor</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,17 +1221,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667576</v>
+        <v>121667582</v>
       </c>
       <c r="B7" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363802</v>
+        <v>363788</v>
       </c>
       <c r="R7" t="n">
-        <v>6388528</v>
+        <v>6388516</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,17 +1328,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667578</v>
+        <v>121667579</v>
       </c>
       <c r="B8" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363780</v>
+        <v>363799</v>
       </c>
       <c r="R8" t="n">
-        <v>6388524</v>
+        <v>6388526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,17 +1435,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667582</v>
+        <v>121667583</v>
       </c>
       <c r="B9" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363788</v>
+        <v>363792</v>
       </c>
       <c r="R9" t="n">
-        <v>6388516</v>
+        <v>6388513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,17 +1542,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667583</v>
+        <v>121667578</v>
       </c>
       <c r="B10" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363792</v>
+        <v>363780</v>
       </c>
       <c r="R10" t="n">
-        <v>6388513</v>
+        <v>6388524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,17 +1649,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667575</v>
+        <v>121667580</v>
       </c>
       <c r="B11" t="n">
-        <v>98144</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,25 +1668,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363843</v>
+        <v>363797</v>
       </c>
       <c r="R11" t="n">
-        <v>6388553</v>
+        <v>6388525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,7 +1745,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1756,17 +1756,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121667577</v>
+        <v>121667576</v>
       </c>
       <c r="B12" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363776</v>
+        <v>363802</v>
       </c>
       <c r="R12" t="n">
-        <v>6388511</v>
+        <v>6388528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -1018,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667585</v>
+        <v>121667584</v>
       </c>
       <c r="B5" t="n">
         <v>92032</v>
@@ -1094,11 +1094,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-04-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1120,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667576</v>
+        <v>121667578</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1165,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363802</v>
+        <v>363780</v>
       </c>
       <c r="R6" t="n">
-        <v>6388528</v>
+        <v>6388524</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1200,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2 plantor</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667575</v>
+        <v>121667576</v>
       </c>
       <c r="B7" t="n">
-        <v>98147</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1239,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363843</v>
+        <v>363802</v>
       </c>
       <c r="R7" t="n">
-        <v>6388553</v>
+        <v>6388528</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1307,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1316,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1340,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667578</v>
+        <v>121667575</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>98147</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,25 +1346,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363780</v>
+        <v>363843</v>
       </c>
       <c r="R8" t="n">
-        <v>6388524</v>
+        <v>6388553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1414,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,6 +1423,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1447,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667577</v>
+        <v>121667580</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1487,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363776</v>
+        <v>363797</v>
       </c>
       <c r="R9" t="n">
-        <v>6388511</v>
+        <v>6388525</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667582</v>
+        <v>121667577</v>
       </c>
       <c r="B10" t="n">
         <v>98113</v>
@@ -1594,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363788</v>
+        <v>363776</v>
       </c>
       <c r="R10" t="n">
-        <v>6388516</v>
+        <v>6388511</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667580</v>
+        <v>121667579</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363797</v>
+        <v>363799</v>
       </c>
       <c r="R11" t="n">
-        <v>6388525</v>
+        <v>6388526</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121667579</v>
+        <v>121667582</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1808,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363799</v>
+        <v>363788</v>
       </c>
       <c r="R12" t="n">
-        <v>6388526</v>
+        <v>6388516</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 15 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121667583</v>
+        <v>121667582</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363792</v>
+        <v>363788</v>
       </c>
       <c r="R4" t="n">
-        <v>6388513</v>
+        <v>6388516</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667584</v>
+        <v>121667578</v>
       </c>
       <c r="B5" t="n">
-        <v>92032</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363685</v>
+        <v>363780</v>
       </c>
       <c r="R5" t="n">
-        <v>6388490</v>
+        <v>6388524</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,12 +1088,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,14 +1118,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667578</v>
+        <v>121667583</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1160,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363780</v>
+        <v>363792</v>
       </c>
       <c r="R6" t="n">
-        <v>6388524</v>
+        <v>6388513</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1205,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,17 +1225,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667576</v>
+        <v>121667584</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>92032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363802</v>
+        <v>363685</v>
       </c>
       <c r="R7" t="n">
-        <v>6388528</v>
+        <v>6388490</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,17 +1302,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 plantor</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667575</v>
+        <v>121667576</v>
       </c>
       <c r="B8" t="n">
-        <v>98147</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,25 +1346,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363843</v>
+        <v>363802</v>
       </c>
       <c r="R8" t="n">
-        <v>6388553</v>
+        <v>6388528</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,7 +1423,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,14 +1434,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667580</v>
+        <v>121667579</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1482,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363797</v>
+        <v>363799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388525</v>
+        <v>6388526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1521,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,14 +1541,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667577</v>
+        <v>121667580</v>
       </c>
       <c r="B10" t="n">
         <v>98113</v>
@@ -1589,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363776</v>
+        <v>363797</v>
       </c>
       <c r="R10" t="n">
-        <v>6388511</v>
+        <v>6388525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1628,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,17 +1648,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667579</v>
+        <v>121667575</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>98147</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,25 +1667,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363799</v>
+        <v>363843</v>
       </c>
       <c r="R11" t="n">
-        <v>6388526</v>
+        <v>6388553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1735,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 15 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,6 +1744,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1756,14 +1756,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121667582</v>
+        <v>121667577</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363788</v>
+        <v>363776</v>
       </c>
       <c r="R12" t="n">
-        <v>6388516</v>
+        <v>6388511</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -1011,14 +1011,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667578</v>
+        <v>121667583</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363780</v>
+        <v>363792</v>
       </c>
       <c r="R5" t="n">
-        <v>6388524</v>
+        <v>6388513</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,17 +1118,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667583</v>
+        <v>121667584</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>92032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363792</v>
+        <v>363685</v>
       </c>
       <c r="R6" t="n">
-        <v>6388513</v>
+        <v>6388490</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,17 +1195,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,17 +1220,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667584</v>
+        <v>121667577</v>
       </c>
       <c r="B7" t="n">
-        <v>92032</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1239,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363685</v>
+        <v>363776</v>
       </c>
       <c r="R7" t="n">
-        <v>6388490</v>
+        <v>6388511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,12 +1297,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1434,17 +1434,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667579</v>
+        <v>121667575</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98147</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,25 +1453,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363799</v>
+        <v>363843</v>
       </c>
       <c r="R9" t="n">
-        <v>6388526</v>
+        <v>6388553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca 15 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,6 +1530,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1541,7 +1542,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1648,17 +1649,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667575</v>
+        <v>121667578</v>
       </c>
       <c r="B11" t="n">
-        <v>98147</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,25 +1668,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363843</v>
+        <v>363780</v>
       </c>
       <c r="R11" t="n">
-        <v>6388553</v>
+        <v>6388524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,7 +1745,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1756,14 +1756,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121667577</v>
+        <v>121667579</v>
       </c>
       <c r="B12" t="n">
         <v>98113</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363776</v>
+        <v>363799</v>
       </c>
       <c r="R12" t="n">
-        <v>6388511</v>
+        <v>6388526</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -1018,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667583</v>
+        <v>121667577</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363792</v>
+        <v>363776</v>
       </c>
       <c r="R5" t="n">
-        <v>6388513</v>
+        <v>6388511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667584</v>
+        <v>121667585</v>
       </c>
       <c r="B6" t="n">
         <v>92032</v>
@@ -1201,6 +1201,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667577</v>
+        <v>121667580</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1267,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363776</v>
+        <v>363797</v>
       </c>
       <c r="R7" t="n">
-        <v>6388511</v>
+        <v>6388525</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1312,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667576</v>
+        <v>121667575</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>98147</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,25 +1351,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363802</v>
+        <v>363843</v>
       </c>
       <c r="R8" t="n">
-        <v>6388528</v>
+        <v>6388553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,6 +1428,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1441,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667575</v>
+        <v>121667578</v>
       </c>
       <c r="B9" t="n">
-        <v>98147</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,25 +1459,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363843</v>
+        <v>363780</v>
       </c>
       <c r="R9" t="n">
-        <v>6388553</v>
+        <v>6388524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1527,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,7 +1536,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1549,7 +1554,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667580</v>
+        <v>121667583</v>
       </c>
       <c r="B10" t="n">
         <v>98113</v>
@@ -1589,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363797</v>
+        <v>363792</v>
       </c>
       <c r="R10" t="n">
-        <v>6388525</v>
+        <v>6388513</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1634,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1661,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667578</v>
+        <v>121667576</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363780</v>
+        <v>363802</v>
       </c>
       <c r="R11" t="n">
-        <v>6388524</v>
+        <v>6388528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1741,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121667582</v>
+        <v>121667576</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363788</v>
+        <v>363802</v>
       </c>
       <c r="R4" t="n">
-        <v>6388516</v>
+        <v>6388528</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667577</v>
+        <v>121667585</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>92032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363776</v>
+        <v>363685</v>
       </c>
       <c r="R5" t="n">
-        <v>6388511</v>
+        <v>6388490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,17 +1088,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667585</v>
+        <v>121667580</v>
       </c>
       <c r="B6" t="n">
-        <v>92032</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363685</v>
+        <v>363797</v>
       </c>
       <c r="R6" t="n">
-        <v>6388490</v>
+        <v>6388525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,17 +1195,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667580</v>
+        <v>121667579</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363797</v>
+        <v>363799</v>
       </c>
       <c r="R7" t="n">
-        <v>6388525</v>
+        <v>6388526</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667575</v>
+        <v>121667577</v>
       </c>
       <c r="B8" t="n">
-        <v>98147</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,25 +1351,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363843</v>
+        <v>363776</v>
       </c>
       <c r="R8" t="n">
-        <v>6388553</v>
+        <v>6388511</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,7 +1428,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1554,7 +1553,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667583</v>
+        <v>121667582</v>
       </c>
       <c r="B10" t="n">
         <v>98113</v>
@@ -1594,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363792</v>
+        <v>363788</v>
       </c>
       <c r="R10" t="n">
-        <v>6388513</v>
+        <v>6388516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1633,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,7 +1660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667576</v>
+        <v>121667583</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1701,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363802</v>
+        <v>363792</v>
       </c>
       <c r="R11" t="n">
-        <v>6388528</v>
+        <v>6388513</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1740,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 plantor</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121667579</v>
+        <v>121667575</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>98147</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,25 +1779,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1808,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363799</v>
+        <v>363843</v>
       </c>
       <c r="R12" t="n">
-        <v>6388526</v>
+        <v>6388553</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1847,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 15 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,6 +1856,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667585</v>
+        <v>121667577</v>
       </c>
       <c r="B5" t="n">
-        <v>92032</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363685</v>
+        <v>363776</v>
       </c>
       <c r="R5" t="n">
-        <v>6388490</v>
+        <v>6388511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,17 +1088,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667579</v>
+        <v>121667578</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363799</v>
+        <v>363780</v>
       </c>
       <c r="R7" t="n">
-        <v>6388526</v>
+        <v>6388524</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 15 plantor</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667577</v>
+        <v>121667575</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>98147</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,25 +1351,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363776</v>
+        <v>363843</v>
       </c>
       <c r="R8" t="n">
-        <v>6388511</v>
+        <v>6388553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,6 +1428,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1446,7 +1447,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667578</v>
+        <v>121667583</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1486,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363780</v>
+        <v>363792</v>
       </c>
       <c r="R9" t="n">
-        <v>6388524</v>
+        <v>6388513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1527,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667582</v>
+        <v>121667584</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>92032</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,25 +1566,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363788</v>
+        <v>363685</v>
       </c>
       <c r="R10" t="n">
-        <v>6388516</v>
+        <v>6388490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,17 +1624,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667583</v>
+        <v>121667582</v>
       </c>
       <c r="B11" t="n">
         <v>98113</v>
@@ -1700,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363792</v>
+        <v>363788</v>
       </c>
       <c r="R11" t="n">
-        <v>6388513</v>
+        <v>6388516</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121667575</v>
+        <v>121667579</v>
       </c>
       <c r="B12" t="n">
-        <v>98147</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363843</v>
+        <v>363799</v>
       </c>
       <c r="R12" t="n">
-        <v>6388553</v>
+        <v>6388526</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,7 +1852,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121667576</v>
+        <v>121667580</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363802</v>
+        <v>363797</v>
       </c>
       <c r="R4" t="n">
-        <v>6388528</v>
+        <v>6388525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667577</v>
+        <v>121667585</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>92046</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363776</v>
+        <v>363685</v>
       </c>
       <c r="R5" t="n">
-        <v>6388511</v>
+        <v>6388490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,17 +1088,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667580</v>
+        <v>121667576</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363797</v>
+        <v>363802</v>
       </c>
       <c r="R6" t="n">
-        <v>6388525</v>
+        <v>6388528</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
         <v>121667578</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667575</v>
+        <v>121667583</v>
       </c>
       <c r="B8" t="n">
-        <v>98147</v>
+        <v>98131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,25 +1351,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363843</v>
+        <v>363792</v>
       </c>
       <c r="R8" t="n">
-        <v>6388553</v>
+        <v>6388513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,7 +1428,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1447,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667583</v>
+        <v>121667579</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363792</v>
+        <v>363799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388513</v>
+        <v>6388526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1526,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667584</v>
+        <v>121667582</v>
       </c>
       <c r="B10" t="n">
-        <v>92032</v>
+        <v>98131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,25 +1565,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363685</v>
+        <v>363788</v>
       </c>
       <c r="R10" t="n">
-        <v>6388490</v>
+        <v>6388516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,12 +1623,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667582</v>
+        <v>121667577</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363788</v>
+        <v>363776</v>
       </c>
       <c r="R11" t="n">
-        <v>6388516</v>
+        <v>6388511</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1740,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121667579</v>
+        <v>121667575</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>98165</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,25 +1779,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363799</v>
+        <v>363843</v>
       </c>
       <c r="R12" t="n">
-        <v>6388526</v>
+        <v>6388553</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 15 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,6 +1856,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121667580</v>
+        <v>121667582</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363797</v>
+        <v>363788</v>
       </c>
       <c r="R4" t="n">
-        <v>6388525</v>
+        <v>6388516</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,17 +1011,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667585</v>
+        <v>121667584</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>92048</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,11 +1096,6 @@
           <t>2024-04-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1118,17 +1113,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667576</v>
+        <v>121667575</v>
       </c>
       <c r="B6" t="n">
-        <v>98131</v>
+        <v>98167</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1132,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363802</v>
+        <v>363843</v>
       </c>
       <c r="R6" t="n">
-        <v>6388528</v>
+        <v>6388553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1200,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,6 +1209,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1225,17 +1221,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667578</v>
+        <v>121667583</v>
       </c>
       <c r="B7" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363780</v>
+        <v>363792</v>
       </c>
       <c r="R7" t="n">
-        <v>6388524</v>
+        <v>6388513</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,17 +1328,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667583</v>
+        <v>121667579</v>
       </c>
       <c r="B8" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363792</v>
+        <v>363799</v>
       </c>
       <c r="R8" t="n">
-        <v>6388513</v>
+        <v>6388526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,17 +1435,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667579</v>
+        <v>121667576</v>
       </c>
       <c r="B9" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363799</v>
+        <v>363802</v>
       </c>
       <c r="R9" t="n">
-        <v>6388526</v>
+        <v>6388528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca 15 plantor</t>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,17 +1542,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667582</v>
+        <v>121667577</v>
       </c>
       <c r="B10" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363788</v>
+        <v>363776</v>
       </c>
       <c r="R10" t="n">
-        <v>6388516</v>
+        <v>6388511</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,17 +1649,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667577</v>
+        <v>121667578</v>
       </c>
       <c r="B11" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363776</v>
+        <v>363780</v>
       </c>
       <c r="R11" t="n">
-        <v>6388511</v>
+        <v>6388524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,17 +1756,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121667575</v>
+        <v>121667580</v>
       </c>
       <c r="B12" t="n">
-        <v>98165</v>
+        <v>98133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363843</v>
+        <v>363797</v>
       </c>
       <c r="R12" t="n">
-        <v>6388553</v>
+        <v>6388525</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,7 +1852,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1868,7 +1863,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121667582</v>
+        <v>121667579</v>
       </c>
       <c r="B4" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363788</v>
+        <v>363799</v>
       </c>
       <c r="R4" t="n">
-        <v>6388516</v>
+        <v>6388526</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667584</v>
+        <v>121667580</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>98140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363685</v>
+        <v>363797</v>
       </c>
       <c r="R5" t="n">
-        <v>6388490</v>
+        <v>6388525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,12 +1088,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,17 +1118,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667575</v>
+        <v>121667578</v>
       </c>
       <c r="B6" t="n">
-        <v>98167</v>
+        <v>98140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363843</v>
+        <v>363780</v>
       </c>
       <c r="R6" t="n">
-        <v>6388553</v>
+        <v>6388524</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1205,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,7 +1214,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,17 +1225,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667583</v>
+        <v>121667582</v>
       </c>
       <c r="B7" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363792</v>
+        <v>363788</v>
       </c>
       <c r="R7" t="n">
-        <v>6388513</v>
+        <v>6388516</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1312,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1328,17 +1332,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667579</v>
+        <v>121667575</v>
       </c>
       <c r="B8" t="n">
-        <v>98133</v>
+        <v>98174</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,25 +1351,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363799</v>
+        <v>363843</v>
       </c>
       <c r="R8" t="n">
-        <v>6388526</v>
+        <v>6388553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca 15 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,6 +1428,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,7 +1440,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1445,7 +1450,7 @@
         <v>121667576</v>
       </c>
       <c r="B9" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,17 +1547,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667577</v>
+        <v>121667585</v>
       </c>
       <c r="B10" t="n">
-        <v>98133</v>
+        <v>92049</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,25 +1566,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363776</v>
+        <v>363685</v>
       </c>
       <c r="R10" t="n">
-        <v>6388511</v>
+        <v>6388490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,17 +1624,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,17 +1654,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667578</v>
+        <v>121667577</v>
       </c>
       <c r="B11" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363780</v>
+        <v>363776</v>
       </c>
       <c r="R11" t="n">
-        <v>6388524</v>
+        <v>6388511</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1741,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,17 +1761,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121667580</v>
+        <v>121667583</v>
       </c>
       <c r="B12" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363797</v>
+        <v>363792</v>
       </c>
       <c r="R12" t="n">
-        <v>6388525</v>
+        <v>6388513</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1848,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1868,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113863803</v>
+        <v>125685234</v>
       </c>
       <c r="B2" t="n">
-        <v>97684</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,53 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>208260</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lönnhult, Vg</t>
+          <t>Lönnhult 1:7, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363686</v>
+        <v>363660</v>
       </c>
       <c r="R2" t="n">
-        <v>6388465</v>
+        <v>6388397</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,24 +749,19 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vinterståndare</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -787,69 +770,76 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Camilla Finsberg</t>
+          <t>Bengt Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Camilla Finsberg</t>
+          <t>Bengt Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117131536</v>
+        <v>113863803</v>
       </c>
       <c r="B3" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lönnhult, 200 m väster om, Vg</t>
+          <t>Lönnhult, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>363733</v>
+        <v>363686</v>
       </c>
       <c r="R3" t="n">
-        <v>6388488</v>
+        <v>6388465</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,24 +863,24 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sannolikt över 100 plantor</t>
+          <t>Vinterståndare</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -899,49 +889,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Aspholmer</t>
+          <t>Camilla Finsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Aspholmer</t>
+          <t>Camilla Finsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121667579</v>
+        <v>121667575</v>
       </c>
       <c r="B4" t="n">
-        <v>98140</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363799</v>
+        <v>363843</v>
       </c>
       <c r="R4" t="n">
-        <v>6388526</v>
+        <v>6388553</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +976,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 15 plantor</t>
+          <t>1 planta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +985,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121667580</v>
+        <v>117131536</v>
       </c>
       <c r="B5" t="n">
-        <v>98140</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,19 +1033,23 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Färnebo, Vg</t>
+          <t>Lönnhult, 200 m väster om, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363797</v>
+        <v>363733</v>
       </c>
       <c r="R5" t="n">
-        <v>6388525</v>
+        <v>6388488</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,17 +1073,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Sannolikt över 100 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,33 +1092,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Lars Aspholmer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Lars Aspholmer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667578</v>
+        <v>121667576</v>
       </c>
       <c r="B6" t="n">
-        <v>98140</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363780</v>
+        <v>363802</v>
       </c>
       <c r="R6" t="n">
-        <v>6388524</v>
+        <v>6388528</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1186,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4 plantor</t>
+          <t>2 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,15 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667582</v>
+        <v>121667577</v>
       </c>
       <c r="B7" t="n">
-        <v>98140</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363788</v>
+        <v>363776</v>
       </c>
       <c r="R7" t="n">
-        <v>6388516</v>
+        <v>6388511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1288,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>Ca 35 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,37 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667575</v>
+        <v>121667578</v>
       </c>
       <c r="B8" t="n">
-        <v>98174</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>363843</v>
+        <v>363780</v>
       </c>
       <c r="R8" t="n">
-        <v>6388553</v>
+        <v>6388524</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1390,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 planta</t>
+          <t>4 plantor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,7 +1399,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1447,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667576</v>
+        <v>121667579</v>
       </c>
       <c r="B9" t="n">
-        <v>98140</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363802</v>
+        <v>363799</v>
       </c>
       <c r="R9" t="n">
-        <v>6388528</v>
+        <v>6388526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1492,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 plantor</t>
+          <t>Ca 15 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,37 +1519,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121667585</v>
+        <v>121667580</v>
       </c>
       <c r="B10" t="n">
-        <v>92049</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363685</v>
+        <v>363797</v>
       </c>
       <c r="R10" t="n">
-        <v>6388490</v>
+        <v>6388525</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,17 +1584,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,15 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667577</v>
+        <v>121667582</v>
       </c>
       <c r="B11" t="n">
-        <v>98140</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363776</v>
+        <v>363788</v>
       </c>
       <c r="R11" t="n">
-        <v>6388511</v>
+        <v>6388516</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1741,7 +1696,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ca 35 plantor</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,12 +1726,7 @@
         <v>121667583</v>
       </c>
       <c r="B12" t="n">
-        <v>98140</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 51423-2024 artfynd.xlsx
+++ b/artfynd/A 51423-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685234</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113863803</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667575</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117131536</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667576</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667577</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667578</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667579</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,6 +1663,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667580</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667582</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,8 +1877,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667583</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>